--- a/marketing_report/outputs/Presupuesto_ROI_Causal/Presupuesto_ROI_Causal_Datos.xlsx
+++ b/marketing_report/outputs/Presupuesto_ROI_Causal/Presupuesto_ROI_Causal_Datos.xlsx
@@ -2482,31 +2482,31 @@
         <v>17</v>
       </c>
       <c r="D2">
-        <v>790</v>
+        <v>871</v>
       </c>
       <c r="E2">
         <v>47387402.9</v>
       </c>
       <c r="F2">
-        <v>17845</v>
+        <v>20087</v>
       </c>
       <c r="G2">
-        <v>951</v>
+        <v>1085</v>
       </c>
       <c r="H2">
-        <v>5.33</v>
+        <v>5.4</v>
       </c>
       <c r="I2">
-        <v>2655.5</v>
+        <v>2359.11</v>
       </c>
       <c r="J2">
-        <v>49829.03</v>
+        <v>43675.03</v>
       </c>
       <c r="K2">
-        <v>169792915</v>
+        <v>196211500</v>
       </c>
       <c r="L2">
-        <v>258.31</v>
+        <v>314.06</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -2520,31 +2520,31 @@
         <v>18</v>
       </c>
       <c r="D3">
-        <v>790</v>
+        <v>871</v>
       </c>
       <c r="E3">
         <v>103390570.59</v>
       </c>
       <c r="F3">
-        <v>110580</v>
+        <v>122118</v>
       </c>
       <c r="G3">
-        <v>727</v>
+        <v>797</v>
       </c>
       <c r="H3">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="I3">
-        <v>934.98</v>
+        <v>846.64</v>
       </c>
       <c r="J3">
-        <v>142215.37</v>
+        <v>129724.68</v>
       </c>
       <c r="K3">
-        <v>125980000</v>
+        <v>137780995</v>
       </c>
       <c r="L3">
-        <v>21.85</v>
+        <v>33.26</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -2558,19 +2558,19 @@
         <v>19</v>
       </c>
       <c r="D4">
-        <v>790</v>
+        <v>871</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>5800</v>
+        <v>6917</v>
       </c>
       <c r="G4">
-        <v>189</v>
+        <v>254</v>
       </c>
       <c r="H4">
-        <v>3.26</v>
+        <v>3.67</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -2579,7 +2579,7 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>42583685</v>
+        <v>54696265</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -2596,19 +2596,19 @@
         <v>20</v>
       </c>
       <c r="D5">
-        <v>790</v>
+        <v>871</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>17870</v>
+        <v>20772</v>
       </c>
       <c r="G5">
-        <v>3685</v>
+        <v>4441</v>
       </c>
       <c r="H5">
-        <v>20.62</v>
+        <v>21.38</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -2617,7 +2617,7 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>652441645</v>
+        <v>790606305</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -2634,19 +2634,19 @@
         <v>17</v>
       </c>
       <c r="D6">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>33.33</v>
+        <v>0</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -2655,7 +2655,7 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>335600</v>
+        <v>0</v>
       </c>
       <c r="L6">
         <v>0</v>
@@ -2672,31 +2672,31 @@
         <v>18</v>
       </c>
       <c r="D7">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="E7">
         <v>1656620.95</v>
       </c>
       <c r="F7">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="G7">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H7">
-        <v>46.15</v>
+        <v>100</v>
       </c>
       <c r="I7">
-        <v>127432.38</v>
+        <v>1656620.95</v>
       </c>
       <c r="J7">
-        <v>276103.49</v>
+        <v>1656620.95</v>
       </c>
       <c r="K7">
-        <v>894700</v>
+        <v>56500</v>
       </c>
       <c r="L7">
-        <v>-45.99</v>
+        <v>-96.59</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -2710,19 +2710,19 @@
         <v>19</v>
       </c>
       <c r="D8">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="G8">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="H8">
-        <v>52.27</v>
+        <v>0</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -2731,7 +2731,7 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>3976300</v>
+        <v>0</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -2748,19 +2748,19 @@
         <v>20</v>
       </c>
       <c r="D9">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="E9">
         <v>0</v>
       </c>
       <c r="F9">
-        <v>53</v>
+        <v>2</v>
       </c>
       <c r="G9">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="H9">
-        <v>71.7</v>
+        <v>100</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -2769,7 +2769,7 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>6430400</v>
+        <v>250000</v>
       </c>
       <c r="L9">
         <v>0</v>
@@ -2968,19 +2968,19 @@
         <v>17</v>
       </c>
       <c r="C2">
-        <v>961</v>
+        <v>1091</v>
       </c>
       <c r="D2">
-        <v>170607520</v>
+        <v>196385765</v>
       </c>
       <c r="E2">
-        <v>951</v>
+        <v>1085</v>
       </c>
       <c r="F2">
-        <v>169792915</v>
+        <v>196211500</v>
       </c>
       <c r="G2">
-        <v>-10</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -2991,19 +2991,19 @@
         <v>18</v>
       </c>
       <c r="C3">
-        <v>784</v>
+        <v>844</v>
       </c>
       <c r="D3">
-        <v>134716625</v>
+        <v>145227530</v>
       </c>
       <c r="E3">
-        <v>727</v>
+        <v>797</v>
       </c>
       <c r="F3">
-        <v>125980000</v>
+        <v>137780995</v>
       </c>
       <c r="G3">
-        <v>-57</v>
+        <v>-47</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -3014,19 +3014,19 @@
         <v>19</v>
       </c>
       <c r="C4">
-        <v>371</v>
+        <v>457</v>
       </c>
       <c r="D4">
-        <v>76039550</v>
+        <v>91387710</v>
       </c>
       <c r="E4">
-        <v>189</v>
+        <v>254</v>
       </c>
       <c r="F4">
-        <v>42583685</v>
+        <v>54696265</v>
       </c>
       <c r="G4">
-        <v>-182</v>
+        <v>-203</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -3037,19 +3037,19 @@
         <v>20</v>
       </c>
       <c r="C5">
-        <v>3776</v>
+        <v>4519</v>
       </c>
       <c r="D5">
-        <v>669356900</v>
+        <v>804128980</v>
       </c>
       <c r="E5">
-        <v>3685</v>
+        <v>4441</v>
       </c>
       <c r="F5">
-        <v>652441645</v>
+        <v>790606305</v>
       </c>
       <c r="G5">
-        <v>-91</v>
+        <v>-78</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -3060,19 +3060,19 @@
         <v>17</v>
       </c>
       <c r="C6">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D6">
-        <v>839000</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>335600</v>
+        <v>0</v>
       </c>
       <c r="G6">
-        <v>-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -3083,19 +3083,19 @@
         <v>18</v>
       </c>
       <c r="C7">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D7">
-        <v>2057300</v>
+        <v>56500</v>
       </c>
       <c r="E7">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>894700</v>
+        <v>56500</v>
       </c>
       <c r="G7">
-        <v>-7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -3106,19 +3106,19 @@
         <v>19</v>
       </c>
       <c r="C8">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>7601200</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>3976300</v>
+        <v>0</v>
       </c>
       <c r="G8">
-        <v>-22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -3129,19 +3129,19 @@
         <v>20</v>
       </c>
       <c r="C9">
-        <v>53</v>
+        <v>2</v>
       </c>
       <c r="D9">
-        <v>8857600</v>
+        <v>250000</v>
       </c>
       <c r="E9">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="F9">
-        <v>6430400</v>
+        <v>250000</v>
       </c>
       <c r="G9">
-        <v>-15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -3274,16 +3274,16 @@
         <v>17</v>
       </c>
       <c r="C2">
-        <v>951</v>
+        <v>1085</v>
       </c>
       <c r="D2">
-        <v>1189</v>
+        <v>1354</v>
       </c>
       <c r="E2">
-        <v>238</v>
+        <v>269</v>
       </c>
       <c r="F2">
-        <v>214615105</v>
+        <v>247389950</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -3294,16 +3294,16 @@
         <v>18</v>
       </c>
       <c r="C3">
-        <v>727</v>
+        <v>797</v>
       </c>
       <c r="D3">
-        <v>904</v>
+        <v>1021</v>
       </c>
       <c r="E3">
-        <v>177</v>
+        <v>224</v>
       </c>
       <c r="F3">
-        <v>158736130</v>
+        <v>178962260</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -3314,16 +3314,16 @@
         <v>19</v>
       </c>
       <c r="C4">
-        <v>189</v>
+        <v>254</v>
       </c>
       <c r="D4">
-        <v>223</v>
+        <v>314</v>
       </c>
       <c r="E4">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="F4">
-        <v>49995375</v>
+        <v>67348700</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -3334,16 +3334,16 @@
         <v>29</v>
       </c>
       <c r="C5">
-        <v>3685</v>
+        <v>4441</v>
       </c>
       <c r="D5">
-        <v>3890</v>
+        <v>4716</v>
       </c>
       <c r="E5">
-        <v>205</v>
+        <v>275</v>
       </c>
       <c r="F5">
-        <v>694068010</v>
+        <v>846480620</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -3354,13 +3354,13 @@
         <v>30</v>
       </c>
       <c r="C6">
-        <v>5552</v>
+        <v>6577</v>
       </c>
       <c r="D6">
-        <v>5552</v>
+        <v>6577</v>
       </c>
       <c r="F6">
-        <v>990798245</v>
+        <v>1179295065</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -3371,16 +3371,16 @@
         <v>17</v>
       </c>
       <c r="C7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>503200</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -3391,16 +3391,16 @@
         <v>18</v>
       </c>
       <c r="C8">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D8">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>1398100</v>
+        <v>56500</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -3411,16 +3411,16 @@
         <v>19</v>
       </c>
       <c r="C9">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="D9">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F9">
-        <v>4311900</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -3431,16 +3431,16 @@
         <v>29</v>
       </c>
       <c r="C10">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="D10">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="E10">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F10">
-        <v>7125100</v>
+        <v>250000</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -3451,13 +3451,13 @@
         <v>30</v>
       </c>
       <c r="C11">
-        <v>69</v>
+        <v>3</v>
       </c>
       <c r="D11">
-        <v>69</v>
+        <v>3</v>
       </c>
       <c r="F11">
-        <v>11637000</v>
+        <v>306500</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -3491,13 +3491,13 @@
         <v>3</v>
       </c>
       <c r="D13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13">
-        <v>920700</v>
+        <v>1163700</v>
       </c>
     </row>
     <row r="14" spans="1:6">
